--- a/moduli_aziende/luppichiniulisse/moduli_compilati/MOD-840-A-Mappatura_Fornitori.xlsx
+++ b/moduli_aziende/luppichiniulisse/moduli_compilati/MOD-840-A-Mappatura_Fornitori.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SW_Gestionali\Suite_9001_v4\moduli_compilati\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simoneleandrini\Documents\GitHub\SG_Viewer\moduli_aziende\luppichiniulisse\moduli_compilati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68B9397-7D97-4C91-B45D-D3AD13DFF1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AFF639-E420-43DD-8C63-2BE68B15F8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -52,102 +52,6 @@
     <t>Sì</t>
   </si>
   <si>
-    <t>Airoldi Metalli spa</t>
-  </si>
-  <si>
-    <t>Alilaser</t>
-  </si>
-  <si>
-    <t>Art.Ing. srl</t>
-  </si>
-  <si>
-    <t>Aviorubber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bossard </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effenne </t>
-  </si>
-  <si>
-    <t>Essinger</t>
-  </si>
-  <si>
-    <t>F.lli Bugli</t>
-  </si>
-  <si>
-    <t>F.lli Pazzaglia</t>
-  </si>
-  <si>
-    <t>Galli e Sesti</t>
-  </si>
-  <si>
-    <t>Galvanica Pasquali</t>
-  </si>
-  <si>
-    <t>GBL</t>
-  </si>
-  <si>
-    <t>Hoffmann</t>
-  </si>
-  <si>
-    <t>Cavicchioli Venio</t>
-  </si>
-  <si>
-    <t>CTS Centro Tecnologico Sperimentale</t>
-  </si>
-  <si>
-    <t>Ma-Inox</t>
-  </si>
-  <si>
-    <t>Metalform</t>
-  </si>
-  <si>
-    <t>Misolet</t>
-  </si>
-  <si>
-    <t>Mochem</t>
-  </si>
-  <si>
-    <t>Mollificio apuano</t>
-  </si>
-  <si>
-    <t>Nuova Fabbris</t>
-  </si>
-  <si>
-    <t>Nuova utensileria</t>
-  </si>
-  <si>
-    <t>Oleoricambi</t>
-  </si>
-  <si>
-    <t>Pastorino</t>
-  </si>
-  <si>
-    <t>Paci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimet Plast </t>
-  </si>
-  <si>
-    <t>Sisoft  </t>
-  </si>
-  <si>
-    <t>Stav    </t>
-  </si>
-  <si>
-    <t>Sama Cromo  </t>
-  </si>
-  <si>
-    <t>Verniciatura industriale    </t>
-  </si>
-  <si>
-    <t>Verniciature Ditta BIRINDELLI PAOLO</t>
-  </si>
-  <si>
-    <t>Z Acciai</t>
-  </si>
-  <si>
     <t>Fornitore materia prima</t>
   </si>
   <si>
@@ -185,6 +89,9 @@
   </si>
   <si>
     <t>Bassa</t>
+  </si>
+  <si>
+    <t>. .  Dato non disponibile in modalità Ospite . .</t>
   </si>
 </sst>
 </file>
@@ -597,16 +504,16 @@
         <v>45916</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -623,19 +530,19 @@
         <v>45916</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <v>49</v>
@@ -649,16 +556,16 @@
         <v>45960</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -675,16 +582,16 @@
         <v>45916</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -701,19 +608,19 @@
         <v>45916</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G6">
         <v>51</v>
@@ -727,16 +634,16 @@
         <v>45916</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -753,16 +660,16 @@
         <v>45916</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -779,16 +686,16 @@
         <v>45916</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -805,16 +712,16 @@
         <v>45916</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -831,19 +738,19 @@
         <v>45916</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G11">
         <v>50</v>
@@ -857,19 +764,19 @@
         <v>45916</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <v>49</v>
@@ -883,16 +790,16 @@
         <v>45916</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -909,19 +816,19 @@
         <v>45916</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G14">
         <v>52</v>
@@ -938,13 +845,13 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
@@ -961,19 +868,19 @@
         <v>45916</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G16">
         <v>54</v>
@@ -987,16 +894,16 @@
         <v>45916</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -1013,19 +920,19 @@
         <v>45916</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G18">
         <v>51</v>
@@ -1039,19 +946,19 @@
         <v>45916</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G19">
         <v>48</v>
@@ -1065,16 +972,16 @@
         <v>45916</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
@@ -1091,19 +998,19 @@
         <v>45916</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>48</v>
@@ -1117,16 +1024,16 @@
         <v>45916</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -1143,19 +1050,19 @@
         <v>45916</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G23">
         <v>51</v>
@@ -1169,16 +1076,16 @@
         <v>45916</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -1195,19 +1102,19 @@
         <v>45916</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G25">
         <v>50</v>
@@ -1221,16 +1128,16 @@
         <v>45916</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -1247,16 +1154,16 @@
         <v>45916</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
         <v>8</v>
@@ -1273,16 +1180,16 @@
         <v>45916</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
         <v>8</v>
@@ -1299,16 +1206,16 @@
         <v>45916</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
         <v>8</v>
@@ -1325,16 +1232,16 @@
         <v>45916</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
@@ -1351,19 +1258,19 @@
         <v>45916</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G31">
         <v>55</v>
@@ -1377,19 +1284,19 @@
         <v>45916</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G32">
         <v>56</v>
@@ -1403,19 +1310,19 @@
         <v>45916</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G33">
         <v>55</v>
